--- a/Exam/gymtrackerpro/lib/controller/__tests__/bbt/workout-session-controller/createWorkoutSession-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/controller/__tests__/bbt/workout-session-controller/createWorkoutSession-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="171">
-  <si>
-    <t>Statement: workout-session-controller.createWorkoutSession(data, exercises) – Server Action. Validates CreateWorkoutSessionInput (memberId non-empty, date ISO, duration 0–180) and workoutSessionExercisesSchema (≥1 exercise, sets 0–6, reps 0–30, weight 0–500). Returns ActionResult&lt;WorkoutSessionWithExercises&gt;.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="244">
+  <si>
+    <t>Statement: createWorkoutSession(session, exercises) – Validates both the session input and the exercises array, then returns an ActionResult&lt;WorkoutSessionWithExercises&gt;. Returns success with the created session and all exercises on success. notes is optional; when omitted or empty the session is still created. Returns a field-level validation error on the session when memberId, date, or duration are invalid. memberId must be a non-empty, non-whitespace-only string. date must be in YYYY-MM-DD format. duration must be 0–180 (inclusive). notes, when provided, must be at most 1024 characters. Returns a failure with message "At least one exercise is required" when the exercises array is empty. Returns a failure with message "Invalid exercises" when any exercise fails per-item validation: exerciseId is required; sets must be 0–6; reps must be 0–30; weight must be 0.0–500.0. Returns a failure with the service error message for NotFoundError and TransactionError.</t>
   </si>
   <si>
     <t/>
@@ -31,27 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: CreateWorkoutSessionInput { memberId, date, duration, notes? } + WorkoutSessionExerciseInput[] (≥1)</t>
+    <t>Input: session: CreateWorkoutSessionInput { memberId: string, date: string, duration: number, notes?: string }, exercises: WorkoutSessionExerciseInput[] { exerciseId: string, sets: number, reps: number, weight: number }[]</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>workoutSessionService.createWorkoutSession is mock-injected</t>
+    <t>memberId: non-empty, non-whitespace-only string (min 1 char after trim). date: YYYY-MM-DD format. duration: integer 0–180 inclusive. notes: optional, max 1024 characters. exercises: at least one element required. Per exercise — sets: 0–6 inclusive; reps: 0–30 inclusive; weight: 0.0–500.0 inclusive.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: ActionResult&lt;WorkoutSessionWithExercises&gt;</t>
+    <t>Output: Promise&lt;ActionResult&lt;WorkoutSessionWithExercises&gt;&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t xml:space="preserve">On success: WorkoutSessionWithExercises returned.
-On validation failure: errors returned.
-On AppError: message returned.</t>
+    <t>On success: session created successfully, returned data matches the created session including all exercises. On session validation failure: field-level validation error returned, the service is not called. On exercise list failure ("At least one exercise is required" or "Invalid exercises"): message-level failure returned, the service is not called. On NotFoundError or TransactionError: operation fails with the service error message.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -66,325 +64,550 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>session data valid</t>
-  </si>
-  <si>
-    <t>memberId non-empty, date ISO, duration 0–180</t>
+    <t>Input validity</t>
+  </si>
+  <si>
+    <t>All session fields valid, one valid exercise → session created successfully, returned data matches the created session</t>
+  </si>
+  <si>
+    <t>Exercise count</t>
+  </si>
+  <si>
+    <t>All session fields valid, two valid exercises → session created successfully, returned data exercises has length 2</t>
+  </si>
+  <si>
+    <t>notes presence</t>
+  </si>
+  <si>
+    <t>notes omitted → session created successfully, returned data notes is null</t>
+  </si>
+  <si>
+    <t>notes value</t>
+  </si>
+  <si>
+    <t>notes: "" (empty string) → session created successfully, returned data notes is ""</t>
+  </si>
+  <si>
+    <t>memberId required</t>
+  </si>
+  <si>
+    <t>memberId omitted → validation fails: memberId field error returned</t>
+  </si>
+  <si>
+    <t>memberId value</t>
+  </si>
+  <si>
+    <t>memberId: "   " (whitespace-only) → validation fails: memberId field error returned</t>
+  </si>
+  <si>
+    <t>date required</t>
+  </si>
+  <si>
+    <t>date omitted → validation fails: date field error returned</t>
+  </si>
+  <si>
+    <t>date format</t>
+  </si>
+  <si>
+    <t>date: "15/06/2024" (DD/MM/YYYY, wrong format) → validation fails: date field error returned</t>
+  </si>
+  <si>
+    <t>duration required</t>
+  </si>
+  <si>
+    <t>duration omitted → validation fails: duration field error returned</t>
+  </si>
+  <si>
+    <t>exercises array</t>
+  </si>
+  <si>
+    <t>exercises: [] (empty array) → operation fails with message "At least one exercise is required"</t>
+  </si>
+  <si>
+    <t>exercise exerciseId</t>
+  </si>
+  <si>
+    <t>exercise with exerciseId omitted → operation fails with message "Invalid exercises"</t>
+  </si>
+  <si>
+    <t>Service error</t>
+  </si>
+  <si>
+    <t>Member does not exist (NotFoundError "Member not found") → operation fails with message "Member not found"</t>
+  </si>
+  <si>
+    <t>A database transaction failure occurs (TransactionError "DB failure") → operation fails with message "DB failure"</t>
+  </si>
+  <si>
+    <t>No TC</t>
+  </si>
+  <si>
+    <t>EC</t>
+  </si>
+  <si>
+    <t>Input Data</t>
+  </si>
+  <si>
+    <t>Expected</t>
+  </si>
+  <si>
+    <t>Actual Result</t>
+  </si>
+  <si>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>all session fields valid, one valid exercise provided, session is created successfully</t>
+  </si>
+  <si>
+    <t>session created successfully, returned data matches the created session</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>EC-2</t>
+  </si>
+  <si>
+    <t>all session fields valid, two valid exercises provided, session is created successfully</t>
+  </si>
+  <si>
+    <t>session created successfully, returned data exercises has length 2</t>
+  </si>
+  <si>
+    <t>EC-3</t>
+  </si>
+  <si>
+    <t>all session fields valid except notes omitted, session is created successfully</t>
+  </si>
+  <si>
+    <t>session created successfully, returned data notes is null</t>
+  </si>
+  <si>
+    <t>EC-4</t>
+  </si>
+  <si>
+    <t>all session fields valid, notes: "" (empty string), session is created successfully</t>
+  </si>
+  <si>
+    <t>session created successfully, returned data notes is ""</t>
+  </si>
+  <si>
+    <t>EC-5</t>
+  </si>
+  <si>
+    <t>all session fields valid, memberId field omitted</t>
+  </si>
+  <si>
+    <t>validation fails: memberId field error returned</t>
+  </si>
+  <si>
+    <t>EC-6</t>
+  </si>
+  <si>
+    <t>all session fields valid, memberId: "   " (whitespace-only)</t>
+  </si>
+  <si>
+    <t>EC-7</t>
+  </si>
+  <si>
+    <t>all session fields valid, date field omitted</t>
+  </si>
+  <si>
+    <t>validation fails: date field error returned</t>
+  </si>
+  <si>
+    <t>EC-8</t>
+  </si>
+  <si>
+    <t>all session fields valid, date: "15/06/2024" (DD/MM/YYYY, wrong format)</t>
+  </si>
+  <si>
+    <t>EC-9</t>
+  </si>
+  <si>
+    <t>all session fields valid, duration field omitted</t>
+  </si>
+  <si>
+    <t>validation fails: duration field error returned</t>
+  </si>
+  <si>
+    <t>EC-10</t>
+  </si>
+  <si>
+    <t>all session fields valid, exercises: [] (empty array)</t>
+  </si>
+  <si>
+    <t>operation fails with message "At least one exercise is required"</t>
+  </si>
+  <si>
+    <t>EC-11</t>
+  </si>
+  <si>
+    <t>all session fields valid, one exercise with exerciseId omitted</t>
+  </si>
+  <si>
+    <t>operation fails with message "Invalid exercises"</t>
+  </si>
+  <si>
+    <t>EC-12</t>
+  </si>
+  <si>
+    <t>all session fields valid, one valid exercise, member does not exist (NotFoundError "Member not found")</t>
+  </si>
+  <si>
+    <t>operation fails with message "Member not found"</t>
+  </si>
+  <si>
+    <t>EC-13</t>
+  </si>
+  <si>
+    <t>all session fields valid, one valid exercise, a database transaction failure occurs (TransactionError "DB failure")</t>
+  </si>
+  <si>
+    <t>operation fails with message "DB failure"</t>
+  </si>
+  <si>
+    <t>Number BVA</t>
+  </si>
+  <si>
+    <t>BVA Test Case</t>
+  </si>
+  <si>
+    <t>memberId length</t>
+  </si>
+  <si>
+    <t>memberId: "" (length 0): empty → validation fails: memberId field error returned</t>
+  </si>
+  <si>
+    <t>memberId: "A" (length 1, min): shortest valid id → session created successfully</t>
+  </si>
+  <si>
+    <t>memberId: "AB" (length 2, min + 1): above minimum → session created successfully</t>
   </si>
   <si>
     <t>duration range</t>
   </si>
   <si>
-    <t>duration ≤ 180</t>
-  </si>
-  <si>
-    <t>duration &gt; 180 → validation error</t>
-  </si>
-  <si>
-    <t>date format</t>
-  </si>
-  <si>
-    <t>ISO YYYY-MM-DD</t>
-  </si>
-  <si>
-    <t>invalid date format → validation error</t>
-  </si>
-  <si>
-    <t>memberId</t>
-  </si>
-  <si>
-    <t>non-empty string</t>
-  </si>
-  <si>
-    <t>empty memberId → validation error</t>
-  </si>
-  <si>
-    <t>exercises array</t>
-  </si>
-  <si>
-    <t>length ≥ 1</t>
-  </si>
-  <si>
-    <t>length = 0 → validation error (message only)</t>
-  </si>
-  <si>
-    <t>exercise sets</t>
-  </si>
-  <si>
-    <t>sets ≤ 6</t>
-  </si>
-  <si>
-    <t>sets &gt; 6 → validation error</t>
-  </si>
-  <si>
-    <t>service outcome</t>
-  </si>
-  <si>
-    <t>resolves WorkoutSessionWithExercises</t>
-  </si>
-  <si>
-    <t>throws NotFoundError → failure</t>
-  </si>
-  <si>
-    <t>throws Error → generic failure</t>
-  </si>
-  <si>
-    <t>No TC</t>
-  </si>
-  <si>
-    <t>EC</t>
-  </si>
-  <si>
-    <t>Input Data</t>
-  </si>
-  <si>
-    <t>Expected</t>
-  </si>
-  <si>
-    <t>Actual Result</t>
-  </si>
-  <si>
-    <t>1,2,4,6,8,10,12</t>
-  </si>
-  <si>
-    <t>VALID_SESSION_INPUT + VALID_EXERCISES, service resolves</t>
-  </si>
-  <si>
-    <t>{ success: true, data: WorkoutSessionWithExercises }</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>{ duration: 181 }, valid exercises</t>
-  </si>
-  <si>
-    <t>{ success: false, errors.duration defined }</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>{ date: "not-a-date" }, valid exercises</t>
-  </si>
-  <si>
-    <t>{ success: false, errors.date defined }</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>{ memberId: "" }, valid exercises</t>
-  </si>
-  <si>
-    <t>{ success: false, errors.memberId defined }</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>valid session data, exercises=[]</t>
-  </si>
-  <si>
-    <t>{ success: false, message defined }</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>valid session, [{ sets: 7 }]</t>
-  </si>
-  <si>
-    <t>{ success: false }</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>valid, service throws NotFoundError</t>
-  </si>
-  <si>
-    <t>{ success: false, message: "Member not found" }</t>
-  </si>
-  <si>
-    <t>valid, service throws WorkoutSessionRequiresExercisesError</t>
-  </si>
-  <si>
-    <t>{ success: false, message from error }</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>valid, service throws Error</t>
-  </si>
-  <si>
-    <t>{ success: false, message: "An unexpected error occurred" }</t>
-  </si>
-  <si>
-    <t>Number BVA</t>
-  </si>
-  <si>
-    <t>BVA Test Case</t>
-  </si>
-  <si>
-    <t>duration boundary</t>
-  </si>
-  <si>
-    <t>duration=180 → valid</t>
-  </si>
-  <si>
-    <t>duration=181 → invalid</t>
-  </si>
-  <si>
-    <t>duration lower</t>
-  </si>
-  <si>
-    <t>duration=0 → valid</t>
-  </si>
-  <si>
-    <t>duration interior</t>
-  </si>
-  <si>
-    <t>duration=1 → valid (min+1)</t>
-  </si>
-  <si>
-    <t>duration=179 → valid (max-1)</t>
-  </si>
-  <si>
-    <t>notes length boundary</t>
-  </si>
-  <si>
-    <t>notes=1023 chars → valid (max-1)</t>
-  </si>
-  <si>
-    <t>sets boundary</t>
-  </si>
-  <si>
-    <t>sets=6 → valid (max)</t>
-  </si>
-  <si>
-    <t>sets=7 → invalid</t>
-  </si>
-  <si>
-    <t>sets interior</t>
-  </si>
-  <si>
-    <t>sets=1 → valid (min+1)</t>
-  </si>
-  <si>
-    <t>sets=5 → valid (max-1)</t>
-  </si>
-  <si>
-    <t>reps interior</t>
-  </si>
-  <si>
-    <t>reps=1 → valid (min+1)</t>
-  </si>
-  <si>
-    <t>reps=29 → valid (max-1)</t>
-  </si>
-  <si>
-    <t>weight interior</t>
-  </si>
-  <si>
-    <t>weight=0.1 → valid (min+0.1)</t>
-  </si>
-  <si>
-    <t>weight=499.9 → valid (max-0.1)</t>
+    <t>duration: -1 (min - 1): below minimum → validation fails: duration field error returned</t>
+  </si>
+  <si>
+    <t>duration: 0 (min): at minimum → session created successfully</t>
+  </si>
+  <si>
+    <t>duration: 1 (min + 1): above minimum → session created successfully</t>
+  </si>
+  <si>
+    <t>duration: 179 (max - 1): below maximum → session created successfully</t>
+  </si>
+  <si>
+    <t>duration: 180 (max): at maximum → session created successfully</t>
+  </si>
+  <si>
+    <t>duration: 181 (max + 1): above maximum → validation fails: duration field error returned</t>
+  </si>
+  <si>
+    <t>notes length</t>
+  </si>
+  <si>
+    <t>notes: "" (length 0): empty string → session created successfully</t>
+  </si>
+  <si>
+    <t>notes: "A" (length 1, min + 1): one character → session created successfully</t>
+  </si>
+  <si>
+    <t>notes: "A".repeat(1023) (max - 1): below maximum → session created successfully</t>
+  </si>
+  <si>
+    <t>notes: "A".repeat(1024) (max): at maximum → session created successfully</t>
+  </si>
+  <si>
+    <t>notes: "A".repeat(1025) (max + 1): above maximum → validation fails: notes field error returned</t>
+  </si>
+  <si>
+    <t>sets range</t>
+  </si>
+  <si>
+    <t>sets: -1 (min - 1): below minimum → operation fails with message "Invalid exercises"</t>
+  </si>
+  <si>
+    <t>sets: 0 (min): at minimum → session created successfully</t>
+  </si>
+  <si>
+    <t>sets: 1 (min + 1): above minimum → session created successfully</t>
+  </si>
+  <si>
+    <t>sets: 5 (max - 1): below maximum → session created successfully</t>
+  </si>
+  <si>
+    <t>sets: 6 (max): at maximum → session created successfully</t>
+  </si>
+  <si>
+    <t>sets: 7 (max + 1): above maximum → operation fails with message "Invalid exercises"</t>
+  </si>
+  <si>
+    <t>reps range</t>
+  </si>
+  <si>
+    <t>reps: -1 (min - 1): below minimum → operation fails with message "Invalid exercises"</t>
+  </si>
+  <si>
+    <t>reps: 0 (min): at minimum → session created successfully</t>
+  </si>
+  <si>
+    <t>reps: 1 (min + 1): above minimum → session created successfully</t>
+  </si>
+  <si>
+    <t>reps: 29 (max - 1): below maximum → session created successfully</t>
+  </si>
+  <si>
+    <t>reps: 30 (max): at maximum → session created successfully</t>
+  </si>
+  <si>
+    <t>reps: 31 (max + 1): above maximum → operation fails with message "Invalid exercises"</t>
+  </si>
+  <si>
+    <t>weight range</t>
+  </si>
+  <si>
+    <t>weight: -0.1 (min - 0.1): below minimum → operation fails with message "Invalid exercises"</t>
+  </si>
+  <si>
+    <t>weight: 0 (min): at minimum → session created successfully</t>
+  </si>
+  <si>
+    <t>weight: 0.1 (min + 0.1): above minimum → session created successfully</t>
+  </si>
+  <si>
+    <t>weight: 499.9 (max - 0.1): below maximum → session created successfully</t>
+  </si>
+  <si>
+    <t>weight: 500 (max): at maximum → session created successfully</t>
+  </si>
+  <si>
+    <t>weight: 500.1 (max + 0.1): above maximum → operation fails with message "Invalid exercises"</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>duration=180</t>
-  </si>
-  <si>
-    <t>{ duration: 180 }</t>
-  </si>
-  <si>
-    <t>success=true</t>
-  </si>
-  <si>
-    <t>duration=181</t>
-  </si>
-  <si>
-    <t>{ duration: 181 }</t>
-  </si>
-  <si>
-    <t>success=false</t>
-  </si>
-  <si>
-    <t>duration=0</t>
-  </si>
-  <si>
-    <t>{ duration: 0 }</t>
-  </si>
-  <si>
-    <t>duration=1</t>
-  </si>
-  <si>
-    <t>{ duration: 1 }</t>
-  </si>
-  <si>
-    <t>duration=179</t>
-  </si>
-  <si>
-    <t>{ duration: 179 }</t>
-  </si>
-  <si>
-    <t>notes=1023</t>
-  </si>
-  <si>
-    <t>{ notes: "a".repeat(1023) }</t>
-  </si>
-  <si>
-    <t>sets=6</t>
-  </si>
-  <si>
-    <t>sets: 6</t>
-  </si>
-  <si>
-    <t>sets=7</t>
-  </si>
-  <si>
-    <t>sets: 7</t>
-  </si>
-  <si>
-    <t>sets=1</t>
-  </si>
-  <si>
-    <t>sets: 1</t>
-  </si>
-  <si>
-    <t>sets=5</t>
-  </si>
-  <si>
-    <t>sets: 5</t>
-  </si>
-  <si>
-    <t>reps=1</t>
-  </si>
-  <si>
-    <t>reps: 1</t>
-  </si>
-  <si>
-    <t>reps=29</t>
-  </si>
-  <si>
-    <t>reps: 29</t>
-  </si>
-  <si>
-    <t>weight=0.1</t>
-  </si>
-  <si>
-    <t>weight: 0.1</t>
-  </si>
-  <si>
-    <t>weight=499.9</t>
-  </si>
-  <si>
-    <t>weight: 499.9</t>
+    <t>BVA-1  (memberId=0)</t>
+  </si>
+  <si>
+    <t>all session fields valid, memberId: "" (empty string)</t>
+  </si>
+  <si>
+    <t>BVA-2  (memberId=1)</t>
+  </si>
+  <si>
+    <t>all session fields valid, memberId: "A" (1 character), session is created successfully</t>
+  </si>
+  <si>
+    <t>session created successfully, returned data memberId is "A"</t>
+  </si>
+  <si>
+    <t>BVA-3  (memberId=2)</t>
+  </si>
+  <si>
+    <t>all session fields valid, memberId: "AB" (2 characters), session is created successfully</t>
+  </si>
+  <si>
+    <t>session created successfully, returned data memberId is "AB"</t>
+  </si>
+  <si>
+    <t>BVA-4  (dur=-1)</t>
+  </si>
+  <si>
+    <t>all session fields valid, duration: -1</t>
+  </si>
+  <si>
+    <t>BVA-5  (dur=0)</t>
+  </si>
+  <si>
+    <t>all session fields valid, duration: 0, session is created successfully</t>
+  </si>
+  <si>
+    <t>session created successfully, returned data duration is 0</t>
+  </si>
+  <si>
+    <t>BVA-6  (dur=1)</t>
+  </si>
+  <si>
+    <t>all session fields valid, duration: 1, session is created successfully</t>
+  </si>
+  <si>
+    <t>session created successfully, returned data duration is 1</t>
+  </si>
+  <si>
+    <t>BVA-7  (dur=179)</t>
+  </si>
+  <si>
+    <t>all session fields valid, duration: 179, session is created successfully</t>
+  </si>
+  <si>
+    <t>session created successfully, returned data duration is 179</t>
+  </si>
+  <si>
+    <t>BVA-8  (dur=180)</t>
+  </si>
+  <si>
+    <t>all session fields valid, duration: 180, session is created successfully</t>
+  </si>
+  <si>
+    <t>session created successfully, returned data duration is 180</t>
+  </si>
+  <si>
+    <t>BVA-9  (dur=181)</t>
+  </si>
+  <si>
+    <t>all session fields valid, duration: 181</t>
+  </si>
+  <si>
+    <t>BVA-10 (notes=0)</t>
+  </si>
+  <si>
+    <t>BVA-11 (notes=1)</t>
+  </si>
+  <si>
+    <t>all session fields valid, notes: "A" (1 character), session is created successfully</t>
+  </si>
+  <si>
+    <t>session created successfully, returned data notes is "A"</t>
+  </si>
+  <si>
+    <t>BVA-12 (notes=1023)</t>
+  </si>
+  <si>
+    <t>all session fields valid, notes: "A".repeat(1023), session is created successfully</t>
+  </si>
+  <si>
+    <t>session created successfully, returned data notes matches the input</t>
+  </si>
+  <si>
+    <t>BVA-13 (notes=1024)</t>
+  </si>
+  <si>
+    <t>all session fields valid, notes: "A".repeat(1024), session is created successfully</t>
+  </si>
+  <si>
+    <t>BVA-14 (notes=1025)</t>
+  </si>
+  <si>
+    <t>all session fields valid, notes: "A".repeat(1025)</t>
+  </si>
+  <si>
+    <t>validation fails: notes field error returned</t>
+  </si>
+  <si>
+    <t>BVA-15 (sets=-1)</t>
+  </si>
+  <si>
+    <t>all session fields valid, one exercise with sets: -1</t>
+  </si>
+  <si>
+    <t>BVA-16 (sets=0)</t>
+  </si>
+  <si>
+    <t>all session fields valid, one exercise with sets: 0, session is created successfully</t>
+  </si>
+  <si>
+    <t>session created successfully</t>
+  </si>
+  <si>
+    <t>BVA-17 (sets=1)</t>
+  </si>
+  <si>
+    <t>all session fields valid, one exercise with sets: 1, session is created successfully</t>
+  </si>
+  <si>
+    <t>BVA-18 (sets=5)</t>
+  </si>
+  <si>
+    <t>all session fields valid, one exercise with sets: 5, session is created successfully</t>
+  </si>
+  <si>
+    <t>BVA-19 (sets=6)</t>
+  </si>
+  <si>
+    <t>all session fields valid, one exercise with sets: 6, session is created successfully</t>
+  </si>
+  <si>
+    <t>BVA-20 (sets=7)</t>
+  </si>
+  <si>
+    <t>all session fields valid, one exercise with sets: 7</t>
+  </si>
+  <si>
+    <t>BVA-21 (reps=-1)</t>
+  </si>
+  <si>
+    <t>all session fields valid, one exercise with reps: -1</t>
+  </si>
+  <si>
+    <t>BVA-22 (reps=0)</t>
+  </si>
+  <si>
+    <t>all session fields valid, one exercise with reps: 0, session is created successfully</t>
+  </si>
+  <si>
+    <t>BVA-23 (reps=1)</t>
+  </si>
+  <si>
+    <t>all session fields valid, one exercise with reps: 1, session is created successfully</t>
+  </si>
+  <si>
+    <t>BVA-24 (reps=29)</t>
+  </si>
+  <si>
+    <t>all session fields valid, one exercise with reps: 29, session is created successfully</t>
+  </si>
+  <si>
+    <t>BVA-25 (reps=30)</t>
+  </si>
+  <si>
+    <t>all session fields valid, one exercise with reps: 30, session is created successfully</t>
+  </si>
+  <si>
+    <t>BVA-26 (reps=31)</t>
+  </si>
+  <si>
+    <t>all session fields valid, one exercise with reps: 31</t>
+  </si>
+  <si>
+    <t>BVA-27 (weight=-0.1)</t>
+  </si>
+  <si>
+    <t>all session fields valid, one exercise with weight: -0.1</t>
+  </si>
+  <si>
+    <t>BVA-28 (weight=0)</t>
+  </si>
+  <si>
+    <t>all session fields valid, one exercise with weight: 0, session is created successfully</t>
+  </si>
+  <si>
+    <t>BVA-29 (weight=0.1)</t>
+  </si>
+  <si>
+    <t>all session fields valid, one exercise with weight: 0.1, session is created successfully</t>
+  </si>
+  <si>
+    <t>BVA-30 (weight=499.9)</t>
+  </si>
+  <si>
+    <t>all session fields valid, one exercise with weight: 499.9, session is created successfully</t>
+  </si>
+  <si>
+    <t>BVA-31 (weight=500)</t>
+  </si>
+  <si>
+    <t>all session fields valid, one exercise with weight: 500, session is created successfully</t>
+  </si>
+  <si>
+    <t>BVA-32 (weight=500.1)</t>
+  </si>
+  <si>
+    <t>all session fields valid, one exercise with weight: 500.1</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -393,87 +616,30 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EP-1</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
-    <t>Valid, duration=180, 1 exercise</t>
-  </si>
-  <si>
-    <t>success=true, session returned</t>
-  </si>
-  <si>
-    <t>EP-2</t>
-  </si>
-  <si>
     <t>BVA-2</t>
   </si>
   <si>
-    <t>success=false, errors defined</t>
-  </si>
-  <si>
-    <t>EP-3</t>
-  </si>
-  <si>
-    <t>Invalid date format</t>
-  </si>
-  <si>
-    <t>EP-4</t>
-  </si>
-  <si>
-    <t>Empty memberId</t>
-  </si>
-  <si>
-    <t>EP-5</t>
-  </si>
-  <si>
-    <t>exercises=[]</t>
-  </si>
-  <si>
-    <t>success=false, message about exercises</t>
-  </si>
-  <si>
-    <t>EP-6</t>
+    <t>BVA-3</t>
+  </si>
+  <si>
+    <t>BVA-4</t>
+  </si>
+  <si>
+    <t>BVA-5</t>
+  </si>
+  <si>
+    <t>BVA-6</t>
+  </si>
+  <si>
+    <t>BVA-7</t>
   </si>
   <si>
     <t>BVA-8</t>
   </si>
   <si>
-    <t>sets=7 in exercise</t>
-  </si>
-  <si>
-    <t>EP-7</t>
-  </si>
-  <si>
-    <t>Service throws NotFoundError</t>
-  </si>
-  <si>
-    <t>success=false, message from error</t>
-  </si>
-  <si>
-    <t>EP-9</t>
-  </si>
-  <si>
-    <t>Service throws unexpected Error</t>
-  </si>
-  <si>
-    <t>success=false, message="An unexpected error occurred"</t>
-  </si>
-  <si>
-    <t>BVA-4</t>
-  </si>
-  <si>
-    <t>BVA-5</t>
-  </si>
-  <si>
-    <t>BVA-6</t>
-  </si>
-  <si>
-    <t>notes=1023 chars</t>
-  </si>
-  <si>
     <t>BVA-9</t>
   </si>
   <si>
@@ -492,6 +658,60 @@
     <t>BVA-14</t>
   </si>
   <si>
+    <t>BVA-15</t>
+  </si>
+  <si>
+    <t>BVA-16</t>
+  </si>
+  <si>
+    <t>BVA-17</t>
+  </si>
+  <si>
+    <t>BVA-18</t>
+  </si>
+  <si>
+    <t>BVA-19</t>
+  </si>
+  <si>
+    <t>BVA-20</t>
+  </si>
+  <si>
+    <t>BVA-21</t>
+  </si>
+  <si>
+    <t>BVA-22</t>
+  </si>
+  <si>
+    <t>BVA-23</t>
+  </si>
+  <si>
+    <t>BVA-24</t>
+  </si>
+  <si>
+    <t>BVA-25</t>
+  </si>
+  <si>
+    <t>BVA-26</t>
+  </si>
+  <si>
+    <t>BVA-27</t>
+  </si>
+  <si>
+    <t>BVA-28</t>
+  </si>
+  <si>
+    <t>BVA-29</t>
+  </si>
+  <si>
+    <t>BVA-30</t>
+  </si>
+  <si>
+    <t>BVA-31</t>
+  </si>
+  <si>
+    <t>BVA-32</t>
+  </si>
+  <si>
     <t>Testing</t>
   </si>
   <si>
@@ -522,16 +742,13 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>WSM-01/WSM-02</t>
+    <t>CTRL-22</t>
   </si>
   <si>
     <t>n/a</t>
   </si>
   <si>
     <t>not yet</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
 </sst>
 </file>
@@ -1047,7 +1264,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1102,13 +1319,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1116,10 +1333,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>1</v>
@@ -1130,13 +1347,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1144,13 +1361,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1158,13 +1375,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1172,13 +1389,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1186,13 +1403,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1200,13 +1417,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1214,13 +1431,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1228,13 +1445,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1242,27 +1459,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1273,7 +1476,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1285,19 +1488,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1305,16 +1508,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1322,16 +1525,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1339,16 +1542,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1356,16 +1559,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1373,16 +1576,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1390,16 +1593,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1407,16 +1610,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1424,16 +1627,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1441,16 +1644,84 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>66</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1461,7 +1732,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1471,13 +1742,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1485,153 +1756,351 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
+      <c r="A3" s="1">
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>1</v>
+      <c r="A9" s="1">
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>90</v>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -1642,7 +2111,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1654,19 +2123,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1674,16 +2143,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1691,16 +2160,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1708,16 +2177,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1725,16 +2194,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1742,16 +2211,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1759,16 +2228,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>94</v>
+        <v>139</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1776,16 +2245,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>106</v>
+        <v>140</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>94</v>
+        <v>142</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1793,16 +2262,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1810,16 +2279,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>110</v>
+        <v>146</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>111</v>
+        <v>147</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1827,16 +2296,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1844,16 +2313,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>94</v>
+        <v>151</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1861,16 +2330,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>94</v>
+        <v>154</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1878,16 +2347,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>119</v>
+        <v>156</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>94</v>
+        <v>154</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1895,16 +2364,322 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>120</v>
+        <v>157</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>121</v>
+        <v>158</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>94</v>
+        <v>159</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>94</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1915,7 +2690,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1928,22 +2703,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>122</v>
+        <v>197</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>123</v>
+        <v>198</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1951,19 +2726,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>124</v>
+        <v>45</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>125</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>126</v>
+        <v>46</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>127</v>
+        <v>47</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>127</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1971,19 +2746,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>128</v>
+        <v>49</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>130</v>
+        <v>51</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>130</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1991,19 +2766,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>131</v>
+        <v>52</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>132</v>
+        <v>53</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>130</v>
+        <v>54</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>130</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2011,19 +2786,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>134</v>
+        <v>56</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>130</v>
+        <v>57</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>130</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2031,19 +2806,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>135</v>
+        <v>58</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>137</v>
+        <v>60</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>137</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2051,19 +2826,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>138</v>
+        <v>61</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>139</v>
+        <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>140</v>
+        <v>62</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2071,19 +2846,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>141</v>
+        <v>63</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>142</v>
+        <v>64</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>143</v>
+        <v>65</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>143</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2091,19 +2866,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>144</v>
+        <v>66</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>145</v>
+        <v>67</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>146</v>
+        <v>65</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2111,19 +2886,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>147</v>
+        <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2131,19 +2906,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>148</v>
+        <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2151,19 +2926,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>149</v>
+        <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2171,19 +2946,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>151</v>
+        <v>1</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2191,19 +2966,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>152</v>
+        <v>1</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2214,16 +2989,16 @@
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>153</v>
+        <v>199</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2234,16 +3009,16 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>154</v>
+        <v>200</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>94</v>
+        <v>128</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2254,16 +3029,16 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>155</v>
+        <v>201</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2274,16 +3049,576 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>94</v>
+      <c r="E27" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -2311,16 +3646,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>157</v>
+        <v>231</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>158</v>
+        <v>232</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>159</v>
+        <v>233</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -2328,45 +3663,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>160</v>
+        <v>234</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>161</v>
+        <v>235</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>162</v>
+        <v>236</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>163</v>
+        <v>237</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>164</v>
+        <v>238</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>165</v>
+        <v>239</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>166</v>
+        <v>240</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>161</v>
+        <v>235</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>162</v>
+        <v>236</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>163</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>167</v>
+      <c r="A3" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="B3" s="1">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="C3" s="1">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -2375,19 +3710,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>168</v>
+        <v>242</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>169</v>
+        <v>243</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>170</v>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
